--- a/ig/ch-epl/StructureDefinition-ch-idmp-clinicalusedefinition-indication.xlsx
+++ b/ig/ch-epl/StructureDefinition-ch-idmp-clinicalusedefinition-indication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CH IDMP ClinicalUseDefinition Indication</t>
+    <t>ClinicalUseDefinition Indication</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T12:35:50+00:00</t>
+    <t>2026-04-07T14:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,7 +262,7 @@
 </t>
   </si>
   <si>
-    <t>CH IDMP ClincalUseDefinition Indication</t>
+    <t>ClincalUseDefinition Indication</t>
   </si>
   <si>
     <t>A single issue - either an indication, contraindication, interaction or an undesirable effect for a medicinal product, medication, device or procedure.</t>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>80</v>
